--- a/public/CuentasCuentas/PagDeRei-CuentasCuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/PagDeRei-CuentasCuentasSeguidas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RMartinez\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\CuentasCuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A51809-4477-4326-A7FB-E367A4C7071B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8E412A-C33B-449E-8DE0-BA7A40C70F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="19">
   <si>
     <t>cuenta</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Por el pago del reintegro a la Tesorería de ingresos de subsidios y subvenciones, en términos de las disposiciones aplicables.</t>
+  </si>
+  <si>
+    <t>Por el pago del reintegro a la Tesorería de ingresos de aportaciones, en términos de las disposiciones aplicables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1.2.05.01 </t>
   </si>
 </sst>
 </file>
@@ -569,7 +575,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -583,7 +589,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -597,7 +603,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -605,13 +611,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -625,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -639,7 +645,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
